--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1233"/>
+  <dimension ref="A1:V1286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83015,6 +83015,3791 @@
       <c r="V1233" t="inlineStr">
         <is>
           <t>The successful candidate should possess a Bachelor’s Degree in Accounting, Finance, or a related field, along with a Certified Public Accountant (CPA) qualification. The candidate should have a minimum of 5 years of proven professional experience in accounting or finance, including significant experience in a Senior Accountant role. Strong accounting, financial management, numerical, analytical, organizational, attention-to-detail, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>6ab76c1596a5f06eb851ec13</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Bule Hora University</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Bule Hora</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1234" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1234" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1234" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1234" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab76c1596a5f06eb851ec13</t>
+        </is>
+      </c>
+      <c r="R1234" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1234" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1234" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1234" t="inlineStr">
+        <is>
+          <t>በዶክተር ኦፍ ሜዲስን (ENT Surgeon ) የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር ዋና ዋና ኃላፊነቶች - ጥራት ያለው እና በምርምር የተደገፈ ትምህርት ለተማሪዎች ማድረስ - የተማሪዎችን የትምህርት እድገት መከታተልና መገምገም - የተማሪዎችን የምርምር ሥራዎች እና የመመረቂያ ጽሑፎችን በዋና አማካሪነት መምራት - በቅድመ-ምረቃ እና በድህረ-ምረቃ ፕሮግራሞች ጥራት ያለው ትምህርት መስጠት - ዘመናዊ እና ተማሪ-ተኮር የማስተማር ስነ-ዘዴዎችን በተግባር ላይ ማዋል - ለተማሪዎች የአካዳሚክና የሙያ ምክር መስጠት</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>6aba6b2739fdfb42295eb8b4</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>የሕግ አገልግሎት ቡድን መሪ</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Hawassa University</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Legal Services; Law</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Hawassa</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I1235" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1235" t="inlineStr">
+        <is>
+          <t>8 years</t>
+        </is>
+      </c>
+      <c r="N1235" t="inlineStr">
+        <is>
+          <t>Birr 21238/Mon</t>
+        </is>
+      </c>
+      <c r="O1235" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1235" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aba6b2739fdfb42295eb8b4</t>
+        </is>
+      </c>
+      <c r="R1235" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1235" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1235" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1235" t="inlineStr">
+        <is>
+          <t>በኮምፓራቲቭ ፐብሊክ ሎው፣ ኢንተርናሽናል ሎው፣ ሌጋል ሰርቪስ፣ ሌጋል ሰርቪስ ማኔጅመንት፣ ሌጋል ሰርቪስ ኦፕሬሽን፣ ሌጋል ስተዲስ፣ ሎዎር ጀነሪክ፣ ፐብሊክ ሎው፣ ኮንሰንትሬሽናል እና ፐብሊክ ሎው፣ ኮምፓራቲቭ ፐብሊክ ሎው እና ጉድ ገቨርናንስ፣ ሎው እና ሎው ሳይንስ፣ ህግ በመጀመሪያ ዲግሪ የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>6ab780045b99590a4547c794</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Bule Hora University</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Bule Hora</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1236" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1236" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1236" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1236" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab780045b99590a4547c794</t>
+        </is>
+      </c>
+      <c r="R1236" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1236" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1236" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1236" t="inlineStr">
+        <is>
+          <t>በማርኬቲንግ ማኔጅመንት በመጀመሪያ ዲግሪ የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር ዋና ዋና ኃላፊነቶች - ጥራት ያለው እና በምርምር የተደገፈ ትምህርት ለተማሪዎች ማድረስ - የተማሪዎችን የትምህርት እድገት መከታተልና መገምገም - የተማሪዎችን የምርምር ሥራዎች እና የመመረቂያ ጽሑፎችን በዋና አማካሪነት መምራት - በቅድመ-ምረቃ እና በድህረ-ምረቃ ፕሮግራሞች ጥራት ያለው ትምህርት መስጠት - ዘመናዊ እና ተማሪ-ተኮር የማስተማር ስነ-ዘዴዎችን በተግባር ላይ ማዋል - ለተማሪዎች የአካዳሚክና የሙያ ምክር መስጠት</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>6aba1ac268a4ba6f49faef11</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Bule Hora University</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>Bule Hora</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1237" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1237" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1237" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1237" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aba1ac268a4ba6f49faef11</t>
+        </is>
+      </c>
+      <c r="R1237" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1237" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1237" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1237" t="inlineStr">
+        <is>
+          <t>በአርክቴክቸር በሁለተኛ ዲግሪ የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>6ab63584139ad84cdb6fa2a4</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Haramaya University</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Haramaya</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1238" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1238" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1238" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1238" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab63584139ad84cdb6fa2a4</t>
+        </is>
+      </c>
+      <c r="R1238" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1238" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1238" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1238" t="inlineStr">
+        <is>
+          <t>Specialization in Prosthodontics, Endodontics, Periodontics, Endodontics and Restorative Dentistry, Orthodontics, Oral and Maxillofacial Surgery, Oral Pathology with relevant work experience Duties and Responsibilities: - Deliver lectures and practical sessions - Develop and update course materials, curricula, and teaching resources. - Conduct research and contribute to academic publications and projects. - Supervise student projects, internships, and research activities. - Evaluate students’ performance and provide academic guidance and mentorship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>0Cfl6Yuwq6SCPp12</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Tender and Registration Officer</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>EMDF INTERNATIONAL PLC</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Business; Supply Chain &amp; Purchasing Management</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1239" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K1239" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1239" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1239" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/0Cfl6Yuwq6SCPp12</t>
+        </is>
+      </c>
+      <c r="R1239" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1239" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1239" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1239" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree in Pharmacy or with related field of study with relevant work experience Duties and Responsibilities - Search for and identify relevant tender opportunities from government institutions, NGOs, private companies, and other organizations. - Review tender documents, eligibility requirements, specifications, deadlines, and evaluation criteria. - Coordinate the preparation of technical, financial, administrative, and supporting documents required for tender submissions. - Ensure tenders are completed accurately and submitted before the specified deadline. - Register the company with government agencies, clients, contractors, suppliers, and relevant procurement portals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>6abcd2481458211401e60e32</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>የሕክምና መሳሪያ ማይክሮባዮሎጂ ቁጥጥር አናሊስት II</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Ethiopian Food and Drug Authority (EFDA)</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Health Care; Health Care Management</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I1240" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1240" t="inlineStr">
+        <is>
+          <t>2 years - 5 years</t>
+        </is>
+      </c>
+      <c r="N1240" t="inlineStr">
+        <is>
+          <t>Birr 19464/Mon</t>
+        </is>
+      </c>
+      <c r="O1240" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1240" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abcd2481458211401e60e32</t>
+        </is>
+      </c>
+      <c r="R1240" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1240" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1240" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1240" t="inlineStr">
+        <is>
+          <t>በማይክሮባዮሎጂ፣ በፋርማሲዩቲካልስ አናሊሲስና ኳሊቲ አሹራንስ፣ ፋርማሲቲካል ማይክሮባዮሎጂ ሁለተኛ ዲግሪ ያለው/ላት አግባብነት ካለው የስራ ልምድ ጋር</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>YLdfMRgDbi0WSHj</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Mathematics Teacher (Primary and High School)</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Addis Global Academy</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1241" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1241" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1241" t="inlineStr">
+        <is>
+          <t>16 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1241" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/YLdfMRgDbi0WSHj</t>
+        </is>
+      </c>
+      <c r="R1241" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1241" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1241" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1241" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Mathematics, Mathematics Education, Education (Mathematics), or a related field of study with relevant teaching experience. Duties &amp; Responsibilities: - Plan and deliver lessons aligned with the school curriculum. - Assess student progress, provide feedback, and maintain accurate records. - Maintain a safe, inclusive, and disciplined classroom. - Support students with different learning needs and abilities. - Communicate with parents and collaborate with fellow teachers. - Participate in school activities, meetings, and professional development. - Follow school policies and safeguard students’ wellbeing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>ROZCpxGAYJbIleh</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Physics Teacher (High school)</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Addis Global Academy</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1242" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1242" t="inlineStr">
+        <is>
+          <t>16 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1242" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/ROZCpxGAYJbIleh</t>
+        </is>
+      </c>
+      <c r="R1242" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1242" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1242" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1242" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Physics, Physics Education, Education (Physics), or a related field of study with relevant teaching experience. Duties &amp; Responsibilities: - Plan and deliver lessons aligned with the school curriculum. - Assess student progress, provide feedback, and maintain accurate records. - Maintain a safe, inclusive, and disciplined classroom. - Support students with different learning needs and abilities. - Communicate with parents and collaborate with fellow teachers. - Participate in school activities, meetings, and professional development. - Follow school policies and safeguard students’ wellbeing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>5s2GA8tXbwkiOwOv</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Geography Teacher (High school)</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Addis Global Academy</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1243" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1243" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1243" t="inlineStr">
+        <is>
+          <t>16 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1243" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/5s2GA8tXbwkiOwOv</t>
+        </is>
+      </c>
+      <c r="R1243" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1243" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1243" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1243" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in Geography, Geography Education, Education (Geography), or a related field of study with relevant teaching experience. Duties &amp; Responsibilities: - Plan and deliver lessons aligned with the school curriculum. - Assess student progress, provide feedback, and maintain accurate records. - Maintain a safe, inclusive, and disciplined classroom. - Support students with different learning needs and abilities. - Communicate with parents and collaborate with fellow teachers. - Participate in school activities, meetings, and professional development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>P2ihQLpH38T6Z6i</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Real Estate Sales Consultant</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Central Hills Real Estate Development</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Business; Business Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1244" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1244" t="inlineStr">
+        <is>
+          <t>1 years</t>
+        </is>
+      </c>
+      <c r="O1244" t="inlineStr">
+        <is>
+          <t>21 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1244" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/P2ihQLpH38T6Z6i</t>
+        </is>
+      </c>
+      <c r="R1244" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1244" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1244" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1244" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in any field of study with relevant work experience. Duties &amp; Responsibilities: - Generate new leads through calls, social media, referrals, networking and personal prospecting. - Present Central Hills properties professionally to prospective buyers. - Conduct client meetings, property presentations and site visits. - Follow up consistently with prospective and existing clients. - Understand customer needs and recommend suitable property options. - Negotiate professionally and support the closing of sales. - Maintain accurate client and sales information in the CRM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>6abe5f06d2e74f314480b16b</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Office Secretary</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Meks Trading Plc</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Business; Secretarial, Admin and Clerical</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1245" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1245" t="inlineStr">
+        <is>
+          <t>29 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1245" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe5f06d2e74f314480b16b</t>
+        </is>
+      </c>
+      <c r="R1245" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1245" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1245" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1245" t="inlineStr">
+        <is>
+          <t>Diploma or Bachelor’s Degree in Secretarial Science, Office Administration,or a related field of study with relevant work experience. Duties &amp; Responsibilities: - Perform general secretarial duties including drafting letters, emails, reports, and meeting minutes. - Manage office communication by answering phone calls, handling inquiries, and directing messages to the appropriate personnel. - Organize and maintain physical and electronic filing systems for documents, records, and reports. - Coordinate schedules, appointments, and meetings for executives and department heads. - Handle office correspondence, mail distribution, and document processing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>6aa53ec76198512a6a13a1ef</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Social Affairs Officer</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>United Nations -Ethiopia</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Finance; Economics</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1246" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1246" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1246" t="inlineStr">
+        <is>
+          <t>About 10 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1246" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aa53ec76198512a6a13a1ef</t>
+        </is>
+      </c>
+      <c r="R1246" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1246" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1246" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1246" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess an advanced university degree (Master’s Degree or equivalent) in International Development, Development Planning, Urban Planning, Economics, Sociology, Social Sciences, or a related field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>6ab3e98b8923733771b3993f</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Quality Assurance and Patient Safety Officer</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Liyana Health Care PLC</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Health Care; General Practitioner</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Hawassa</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1247" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1247" t="inlineStr">
+        <is>
+          <t>1 years</t>
+        </is>
+      </c>
+      <c r="O1247" t="inlineStr">
+        <is>
+          <t>About 10 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1247" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab3e98b8923733771b3993f</t>
+        </is>
+      </c>
+      <c r="R1247" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1247" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1247" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1247" t="inlineStr">
+        <is>
+          <t>LIYANA HEALTH CARE Plc. seeks a Quality Assurance and Patient Safety Officer for Yanet Primary Hospital in Hawassa. The role requires a General Practitioner or a health science graduate with a Master’s degree, plus at least one year of experience in healthcare quality management. Candidates must hold valid registration and licensing certificates, possess professional certifications such as ISO 9001, and demonstrate proficiency in audit tools, QI methodologies (PDSA), risk analysis, and documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>6a9712cd87465948ffdfe223</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Battery Hardware Team Lead/Engineer</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Dodai Manufacturing</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Engineering; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1248" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1248" t="inlineStr">
+        <is>
+          <t>3 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1248" t="inlineStr">
+        <is>
+          <t>About 10 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1248" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9712cd87465948ffdfe223</t>
+        </is>
+      </c>
+      <c r="R1248" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1248" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1248" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1248" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Mechanical Engineering, Electrical Engineering, Mechatronics, or a related field, along with 3–5 years of relevant professional experience in Mechanical Engineering, battery systems, or a related technical field. The candidate should demonstrate strong technical knowledge and problem-solving skills, with the ability to work with mechanical and electrical systems, support battery system operations, troubleshoot technical issues, and contribute to maintenance, testing, and system improvement activities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>6ab2984c1f1f9b71ed717fa9</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>CALL CENTER REPRESENTATIVE (RECEPTIONIST)</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>FG BUSINESS GROUP</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Business; Business Administration</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1249" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1249" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1249" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1249" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab2984c1f1f9b71ed717fa9</t>
+        </is>
+      </c>
+      <c r="R1249" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1249" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1249" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1249" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree or Diploma in Business Administration, Management, Marketing, Communications, Customer Service, Secretarial Science, or a related field. The candidate should have a minimum of 2 years of relevant professional experience in call center operations, reception, customer service, front-desk, or administrative work. Strong communication, customer service, interpersonal, organizational, coordination, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>6ab298034eefb2731378bd5e</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Graphic/Motion Designer</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Temer Properties</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Creative Arts; Graphic Design</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1250" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1250" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1250" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1250" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab298034eefb2731378bd5e</t>
+        </is>
+      </c>
+      <c r="R1250" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1250" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1250" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1250" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Diploma or Certificate in Graphic Design, Multimedia, or a related field. The candidate should have at least 3 years of proven professional experience as a Graphic Designer, with a strong portfolio demonstrating expertise in branding, digital content, and campaign materials. Strong creative, visual design, communication, attention-to-detail, and time-management skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>6aba56e67f6fbb1d42f8f052</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>SECRETARY AND OFFICE ADMINISTRATOR</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>HAKID ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Business; Business Administration</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1251" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K1251" t="inlineStr">
+        <is>
+          <t>1 years</t>
+        </is>
+      </c>
+      <c r="O1251" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1251" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aba56e67f6fbb1d42f8f052</t>
+        </is>
+      </c>
+      <c r="R1251" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1251" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1251" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1251" t="inlineStr">
+        <is>
+          <t>TVET 10+4 or Bachelor's degree in Secretarial Science and Office Management or an equivalent qualification is proreferred or relative filed of study with relevant work experience out of Experience: Minimum of 1 (one) year and above of proven experience as a Secretary or Administrative Assistant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>6ab68c89efe7584af52a15be</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Monitoring, Evaluation and Learning (MEL) Coordinator - Oromia Region</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Global Communities</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Natural Science; Statistics</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1252" t="inlineStr">
+        <is>
+          <t>8 years</t>
+        </is>
+      </c>
+      <c r="O1252" t="inlineStr">
+        <is>
+          <t>2 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1252" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab68c89efe7584af52a15be</t>
+        </is>
+      </c>
+      <c r="R1252" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1252" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1252" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1252" t="inlineStr">
+        <is>
+          <t>The role is for a Monitoring, Evaluation and Learning (MEL) Coordinator in the Oromia Region of Ethiopia. Candidates must hold an undergraduate degree in a related field with at least eight years of relevant experience, including five years of MEL work in donor‑funded projects. The position focuses on designing and implementing robust MEL systems, managing data collection and analysis, building capacity among staff and partners, and fostering a culture of evidence‑based decision making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>6a99375fdc86850c7785036c</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Senior Compounding / Mixer Machine Operator</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Lesso Ethiopia Trading PLC</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Engineering; Chemical Engineering</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1253" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1253" t="inlineStr">
+        <is>
+          <t>3 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1253" t="inlineStr">
+        <is>
+          <t>2 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1253" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a99375fdc86850c7785036c</t>
+        </is>
+      </c>
+      <c r="R1253" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1253" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1253" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1253" t="inlineStr">
+        <is>
+          <t>The position requires a BSC degree in Chemical or related fields, or a Diploma in General Mechanics/Electricity. Applicants must have 3 to 5 years of experience in plastic manufacturing and be able to operate compounding/mixer machines efficiently. Candidates should submit their application as a single PDF via email or in hard copy at the specified headquarters location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>6a998b94f75c370a98d1316e</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Talent Search - Ethiojobs</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Business; Marketing Management</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1254" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1254" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="O1254" t="inlineStr">
+        <is>
+          <t>2 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1254" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a998b94f75c370a98d1316e</t>
+        </is>
+      </c>
+      <c r="R1254" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1254" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1254" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1254" t="inlineStr">
+        <is>
+          <t>The Marketing Manager will design and execute comprehensive marketing strategies that align with the company’s business goals. Responsibilities include brand development, digital and offline campaigns, lead generation, market research, and customer engagement initiatives. The role requires a bachelor’s degree in a related field, at least six years of professional marketing experience, and 2–3 years in a managerial capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>6a998c12d10a820a980c29e8</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Network of Ethiopian Women Association (NEWA)</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Social Science; Social Development</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1255" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1255" t="inlineStr">
+        <is>
+          <t>7 years</t>
+        </is>
+      </c>
+      <c r="O1255" t="inlineStr">
+        <is>
+          <t>2 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1255" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a998c12d10a820a980c29e8</t>
+        </is>
+      </c>
+      <c r="R1255" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1255" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1255" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1255" t="inlineStr">
+        <is>
+          <t>The Project Coordinator will manage the daily coordination and implementation of the CSIF-supported Women Led Organizations Initiative in Addis Ababa, Ethiopia. This role requires a master’s degree in Development Studies or related fields, 7+ years of experience coordinating multi‑partner projects, and strong skills in advocacy, capacity strengthening, monitoring &amp; evaluation, and financial oversight. Fluency in English and Amharic is essential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>6a9a88ca90a330635bc5ba76</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Sales invoice officer</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Chora Gas and Chemical Product Factory</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Business; Marketing Management</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1256" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1256" t="inlineStr">
+        <is>
+          <t>3 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1256" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9a88ca90a330635bc5ba76</t>
+        </is>
+      </c>
+      <c r="R1256" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1256" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1256" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1256" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a College Diploma in Marketing Management, Accounting, or a related field, with a minimum of 2 years of relevant professional experience in sales invoicing. The candidate should demonstrate good knowledge of sales invoicing procedures, invoice preparation, documentation, record keeping, and financial transaction processing. Strong numerical, organizational, attention-to-detail, communication, and computer skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>6abba90399a71b6fd3ceff51</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Radisson Blu Hotel Addis Ababa</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Engineering; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1257" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1257" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1257" t="inlineStr">
+        <is>
+          <t>3 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1257" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abba90399a71b6fd3ceff51</t>
+        </is>
+      </c>
+      <c r="R1257" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1257" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1257" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1257" t="inlineStr">
+        <is>
+          <t>BA degree Mechanical /Electrical engineer or other related field of study with relevant work experience out of with Minimum of three years’ work experience as a general maintenance technician in a four or five star hotels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>6a99615c5b89ad48535dbc91</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>ISHDO Job Vacancy 2026 | Community Outreach Health Care Worker (12 Positions – Fresh Graduats)</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Integrated Service on Health and Development Organization</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Health Care; Nursing</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I1258" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1258" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1258" t="inlineStr">
+        <is>
+          <t>3 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1258" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a99615c5b89ad48535dbc91</t>
+        </is>
+      </c>
+      <c r="R1258" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1258" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1258" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1258" t="inlineStr">
+        <is>
+          <t>Integrated Service on Health and Development Organization (ISHDO) seeks fresh graduates with a Bachelor’s degree in Nursing or Public Health to join its Community Breast Cancer Awareness project. The role focuses on raising awareness, facilitating community dialogues, and supporting early detection and referral of breast cancer cases within rural kebeles and health posts across three Ethiopian zones. Candidates should be willing to travel frequently, possess basic digital and reporting skills, and demonstrate strong communication and teamwork abilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>6aad283787280c4f2a583170</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Sales Agronomist</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>KKGT Import Export</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Natural Science; Agricultural Science</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1259" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1259" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1259" t="inlineStr">
+        <is>
+          <t>3 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1259" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aad283787280c4f2a583170</t>
+        </is>
+      </c>
+      <c r="R1259" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1259" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1259" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1259" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor of Science (BSc) Degree in Plant Science, Agronomy, Agricultural Sciences, or a related field. The candidate should have a minimum of 2 years of relevant professional work experience. Strong knowledge of agricultural practices, crop production, plant science, and farm operations, along with strong analytical, technical, organizational, teamwork, and problem-solving skills, is also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>6abccfa796f2c70ee805137c</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Office Engineer</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Hebron Construction &amp; Trading W.L.L.</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Engineering; Civil Engineering</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1260" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1260" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1260" t="inlineStr">
+        <is>
+          <t>4 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1260" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abccfa796f2c70ee805137c</t>
+        </is>
+      </c>
+      <c r="R1260" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1260" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1260" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1260" t="inlineStr">
+        <is>
+          <t>The position seeks a BSc Civil Engineering graduate with at least five years of experience as an office engineer in a construction company. The role is based at Hebron Construction PLC’s Addis Ababa head office and requires strong administrative, coordination, and documentation skills to support project delivery. Candidates will work closely with engineering teams, manage office operations, and ensure compliance with safety and quality standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>6abe4c04105ae818c6e984ec</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Human Resources Supervisor</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>M/S Hussein Seid Proprietor</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Business; Human Resource Management</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1261" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1261" t="inlineStr">
+        <is>
+          <t>3 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1261" t="inlineStr">
+        <is>
+          <t>5 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1261" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4c04105ae818c6e984ec</t>
+        </is>
+      </c>
+      <c r="R1261" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1261" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1261" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1261" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Human Resources Management, Business Administration, Management, or a related field of study with relevant work experience out of 3–5 years of relevant HR experience, preferably in a manufacturing or industrial company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>6abe4c0d4a710318c6dbb449</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>M/S Hussein Seid Proprietor</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Engineering; Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1262" t="inlineStr">
+        <is>
+          <t>3 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1262" t="inlineStr">
+        <is>
+          <t>5 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1262" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4c0d4a710318c6dbb449</t>
+        </is>
+      </c>
+      <c r="R1262" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1262" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1262" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1262" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Electrical Engineering, Mechanical Engineering, Industrial Engineering, Operations Management, or a related field of study with relevant work experience out of with 3–5 years of relevant experience, preferably in a manufacturing or industrial environment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>6abd247004ac1b039afbce66</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Monitoring Evaluation accountability and learning (MEAL) Advisor</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Integrated Service on Health and Development Organization</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Health Care; Public Health</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1263" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1263" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1263" t="inlineStr">
+        <is>
+          <t>5 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1263" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd247004ac1b039afbce66</t>
+        </is>
+      </c>
+      <c r="R1263" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1263" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1263" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1263" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Master’s Degree in Monitoring and Evaluation, Public Health, Epidemiology, Statistics, Health Informatics, or a related field. The candidate should have a minimum of 5 years of progressive professional experience in Monitoring and Evaluation (M&amp;E) or Monitoring, Evaluation, and Learning (MEL), preferably within HIV/AIDS, public health, or community health programs. Strong monitoring and evaluation, data analysis, reporting, analytical, organizational, communication, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>6abe4bfb0a548618c60f8a58</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Senior Technician</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>M/S Hussein Seid Proprietor</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Engineering; Electromechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1264" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1264" t="inlineStr">
+        <is>
+          <t>3 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1264" t="inlineStr">
+        <is>
+          <t>5 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1264" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4bfb0a548618c60f8a58</t>
+        </is>
+      </c>
+      <c r="R1264" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1264" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1264" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1264" t="inlineStr">
+        <is>
+          <t>Diploma or Bachelor’s degree in Electrical Engineering, Electromechanical Engineering, Mechanical Engineering, or a related technical field of study with relevant work experience out of with 3–5 years of relevant industrial experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>6a9ed1bfb326a83dfedccd29</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>ፅሐፊ (Secretary)</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>A and M Engineering</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Business; Secretarial, Admin and Clerical</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1265" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1265" t="inlineStr">
+        <is>
+          <t>1 years</t>
+        </is>
+      </c>
+      <c r="O1265" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1265" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9ed1bfb326a83dfedccd29</t>
+        </is>
+      </c>
+      <c r="R1265" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1265" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1265" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1265" t="inlineStr">
+        <is>
+          <t>ይህ ተግባር ከፈለጉት በኢቲው እና የቤት ስራዎች ጋር ዝቅተኛ ደረጃ ነው። ተሞልቶ ወደ ቢሮ የሚጠቀሙትን መረጃዎች እና የገቢ/ወጪ ማስታወቂያዎች ይተካሉ። በነባሪ ደረጃ አምልኮ ይሆናል።</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>6abcf4c86d6cde409cfba352</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>አካውንታንት II</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Ethiopian Food and Drug Authority (EFDA)</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Finance; Accounting</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Hawassa</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1266" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="N1266" t="inlineStr">
+        <is>
+          <t>Birr 13732/Mon</t>
+        </is>
+      </c>
+      <c r="O1266" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1266" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abcf4c86d6cde409cfba352</t>
+        </is>
+      </c>
+      <c r="R1266" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1266" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1266" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1266" t="inlineStr">
+        <is>
+          <t>በአካውንቲንግ፣ አካውንቲንግ ኤንድ ኦዲቲንግ፣ አካውቲንግ ኤንድ በጀት፣ ባንኪንግና ፋይናንስ፣ ኮምፒዩተራይዝድ አካውንቲንግ፣ ኮኦፕሬቲቭ አካውንቲንግ፣ አካውንቲንግና ፋይናንስ፣ ፋይናንሻል አካውንቲንግ፣ ፐብሊክ ፋይናንስ፣ አካውንቲንግና ፐብሊክ ፋይናንስ፣ ኮኦፕሬቲቭ አካውንቲንግ ኤንድ ኦዲቲንግ፣ አካውንቲንግና በጀት ሰርቪስ፣ ፐብሊክ ሴክተር ፋይናንስ፣ አካውንቲንግና በጀት ሰፖርት፣ ኮሜርስ አካውንቲንግ፣ ፋይናንስ ዲቬሎፕመንት ኢኮኖሚክስ፣ ፋይናንሻል ማኔጅመንት፣ ፐብሊክ ፋይናንሻል ማኔጅመንት፣ መንግስት ፋይናንስ አስተዳደር፣ ሰርቲፋይድ አካውንቲንግ፣ ታክስ አስተዳደር፣ ታክስና ከስተም አድሚኒስትሬሽን ማኔጅመንት በመጀመሪያ ዲግሪ የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>6a9ed1acc1b30b3e98cb7bfc</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Cook II</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Afro Education and Training Development P.L.C</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Hospitality; Food Preparation</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1267" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1267" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1267" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9ed1acc1b30b3e98cb7bfc</t>
+        </is>
+      </c>
+      <c r="R1267" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1267" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1267" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1267" t="inlineStr">
+        <is>
+          <t>This position requires a TVET Level II/III Certificate or Diploma in Food Preparation/Culinary Arts (or equivalent culinary training). The role involves solid proficiency in hot/cold line cooking, prep work, bulk food preparation and adherence to standard recipes. Candidates must have strong knowledge of HACCP standards, correct holding temperatures, cross‑contamination prevention and sanitation guidelines. The job demands speed, consistency and effective communication with commis chefs, stewards and the head chef during high‑volume rush periods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>6abe4be264706718c6476753</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Sales Person / Sales Officer</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Mohammed Lalo Import and Export</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Business; Marketing Management</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1268" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1268" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1268" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1268" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4be264706718c6476753</t>
+        </is>
+      </c>
+      <c r="R1268" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1268" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1268" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1268" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Marketing Management, Business Administration, Food Engineering, or a related field. The candidate should have a minimum of 2 years of proven professional experience in sales or marketing, preferably within the food industry, Fast-Moving Consumer Goods (FMCG), or bakery ingredients sector. Strong sales, marketing, communication, customer relationship management, negotiation, organizational, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>6abe4ba9bc09f718c6fe8de9</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Senior Structural Engineer /BIM Temporary /Formwork Structural Engineering )</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Ethiopian Construction Works Corporation</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Engineering; Structural Engineering</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1269" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1269" t="inlineStr">
+        <is>
+          <t>2 years - 4 years</t>
+        </is>
+      </c>
+      <c r="O1269" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1269" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4ba9bc09f718c6fe8de9</t>
+        </is>
+      </c>
+      <c r="R1269" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1269" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1269" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1269" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess an MSc or BSc Degree in Structural Engineering or a related field. The candidate should have 2–4 years of relevant professional experience, with practical experience in detailed formwork design for slabs, beams, columns, walls, cores, foundations, shoring and re-shoring systems, jump-form and climbing systems, and other specialized structures. Strong structural design, formwork engineering, technical, analytical, attention-to-detail, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>6abe4bac80683218c6088e23</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Junior Mechanical Engineer</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Ethiopian Construction Works Corporation</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Engineering; Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1270" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1270" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1270" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1270" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4bac80683218c6088e23</t>
+        </is>
+      </c>
+      <c r="R1270" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1270" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1270" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1270" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor of Science (BSc) Degree in Mechanical Engineering. No prior professional work experience is required, making the position suitable for fresh graduates and entry-level candidates. Strong mechanical engineering knowledge and proficiency in AutoCAD, along with technical, analytical, problem-solving, and teamwork skills, are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>6a9ed197f15acf3dfe687bf0</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>F&amp;B Controller (Food &amp; Beverage Cost Controller)</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Afro Education and Training Development P.L.C</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Finance; Accounting</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1271" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1271" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1271" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1271" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9ed197f15acf3dfe687bf0</t>
+        </is>
+      </c>
+      <c r="R1271" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1271" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1271" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1271" t="inlineStr">
+        <is>
+          <t>The position requires a bachelor’s degree or diploma in Accounting, Finance, Hospitality Management, Business Administration, or a related field. Candidates must have 3–5+ years of dedicated experience managing food and beverage cost control in high-volume catering, hotels, banquets, or multi-outlet restaurant operations. The role demands strong competencies in recipe costing, inventory auditing, purchasing oversight, waste and yield analysis, POS/ERP proficiency, and advanced Excel reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>6a9fcf051c26bc1413c143db</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Sales Executive – Solar Water Pumps &amp; Motors Specialist</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Sibhatu General Trading PLC</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Business; Marketing Management</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1272" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1272" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1272" t="inlineStr">
+        <is>
+          <t>7 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1272" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9fcf051c26bc1413c143db</t>
+        </is>
+      </c>
+      <c r="R1272" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1272" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1272" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1272" t="inlineStr">
+        <is>
+          <t>Sibhatu General Trading PLC seeks a motivated Sales Executive to promote and sell solar water pumps, electric motors, submersible pumps, generators, and related electrical accessories. The role involves identifying new customers, maintaining relationships, preparing quotations, and meeting monthly sales targets. Candidates should have experience in sales—preferably within solar or electrical products—and strong communication skills. A valid driving license is advantageous for customer visits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>6abccfa236424b0ee83a28c9</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Junior Accountant</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Ethiopian Catholic Church Social Development Coordinating Office</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Finance; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1273" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1273" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1273" t="inlineStr">
+        <is>
+          <t>8 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1273" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abccfa236424b0ee83a28c9</t>
+        </is>
+      </c>
+      <c r="R1273" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1273" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1273" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1273" t="inlineStr">
+        <is>
+          <t>The position is for a Junior Accountant at the Catholic Caritas Ethiopia Branch Office of Addis Ababa, Daughters of Charity Development Coordinating Office (DOC). Candidates must hold a BA degree in accounting or finance and have 3 years’ experience. The role involves recording, classifying, posting, reconciling, and reporting financial transactions, preparing statements for donors, ensuring compliance with regulations, and supporting branch offices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>6abd4e6c2c5abe3a0fda1fd0</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Finished Goods Store Keeper</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Majet Foods Trading One Member PLC</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Finance; Accounting</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1274" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1274" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1274" t="inlineStr">
+        <is>
+          <t>8 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1274" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd4e6c2c5abe3a0fda1fd0</t>
+        </is>
+      </c>
+      <c r="R1274" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1274" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1274" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1274" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Accounting, Accounting and Finance, Management, Economics, or a related field. The candidate should have a minimum of 5 years of progressive professional experience as a Finished Goods Storekeeper, preferably with significant experience in a food production company or a related manufacturing environment. Strong inventory management, warehouse operations, stock control, numerical, organizational, attention-to-detail, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>6aba570aa348301d42a94472</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Senior Manager – Service &amp; Parts</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Talent Search - Ethiojobs</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Engineering; Automotive Engineering</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1275" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1275" t="inlineStr">
+        <is>
+          <t>7 years</t>
+        </is>
+      </c>
+      <c r="O1275" t="inlineStr">
+        <is>
+          <t>8 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1275" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aba570aa348301d42a94472</t>
+        </is>
+      </c>
+      <c r="R1275" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1275" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1275" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1275" t="inlineStr">
+        <is>
+          <t>The Senior Manager – Service &amp; Parts will lead the development and management of aftermarket operations for two‑wheelers and three‑wheelers across Ethiopia. Candidates should hold a bachelor’s degree in mechanical or automobile engineering and have at least seven years of experience in service and parts functions, with supervisory exposure. Strong technical knowledge of both internal combustion and electric vehicle systems, combined with local market expertise, is essential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>6abd245b371be3039aa93a7c</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Executive Assistant</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>National Election Board of Ethiopia (NEBE)</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Business; Secretarial, Admin and Clerical</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1276" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1276" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="O1276" t="inlineStr">
+        <is>
+          <t>8 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1276" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd245b371be3039aa93a7c</t>
+        </is>
+      </c>
+      <c r="R1276" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1276" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1276" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1276" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s or Master’s Degree in Management, Secretarial and Office Management, Public Administration, Law, Political Science, or a related field. The candidate should have 2–4 years of relevant professional experience. Strong administrative, organizational, communication, interpersonal, analytical, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>6abe4c075ecf0918c6ebed6a</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Senior Labor Marketing Officer</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>AMG Holdings PLC</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Business; Marketing Management</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Gelan</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1277" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1277" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="O1277" t="inlineStr">
+        <is>
+          <t>9 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1277" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4c075ecf0918c6ebed6a</t>
+        </is>
+      </c>
+      <c r="R1277" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1277" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1277" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1277" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Business Management, Human Resource Management, or a related field. The candidate should have the ability to collect, analyze, and report labor market information to support employment programs, workforce planning, and organizational decision-making. Strong labor market analysis, data collection, analytical, reporting, communication, organizational, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>6abe4beb5149cc18c6c1dcc2</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Motorist</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>AMG Holdings PLC</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Logistics; Motor Bike Drivers License</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Gelan</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1278" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1278" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1278" t="inlineStr">
+        <is>
+          <t>9 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1278" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4beb5149cc18c6c1dcc2</t>
+        </is>
+      </c>
+      <c r="R1278" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1278" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1278" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1278" t="inlineStr">
+        <is>
+          <t>The successful candidate should have completed at least Grade 10 or Grade 12 and possess a valid Ethiopian driving license, Grade 3 for light vehicles, or the appropriate motorcycle license for two-wheeled vehicle roles. The candidate should have a minimum of 2 years of relevant professional driving experience and demonstrate safe and responsible operation of company vehicles. Strong driving, road-safety, communication, reliability, responsibility, and attention-to-detail skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>6abd2424eec35d039a6a0d06</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Information Technology (IT) expertise</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Unlimited Packaging PLC</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>ICT; Computer Science and Information Technology</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1279" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1279" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="O1279" t="inlineStr">
+        <is>
+          <t>12 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1279" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd2424eec35d039a6a0d06</t>
+        </is>
+      </c>
+      <c r="R1279" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1279" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1279" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1279" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree from a recognized educational institution in Information Technology (IT), Computer Science, Software Engineering, Computer Engineering, Information Systems, or a related field. The candidate should have a minimum of 4 years of relevant professional experience. Strong technical, analytical, software, communication, organizational, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>6aaa84ffb3d68836de9b4e17</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>BARMAN</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Inter Luxury Hotel</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Hospitality; Hotel Management</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1280" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1280" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1280" t="inlineStr">
+        <is>
+          <t>14 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1280" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aaa84ffb3d68836de9b4e17</t>
+        </is>
+      </c>
+      <c r="R1280" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1280" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1280" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1280" t="inlineStr">
+        <is>
+          <t>The successful candidate should ideally possess a relevant Degree, Diploma, or Certificate in Hospitality, Tourism Management, or a related field. The candidate should have previous professional experience working as a Barman. Good grooming, a professional appearance, strong customer service, communication, interpersonal, and teamwork skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>6aac008eca3b4140b280b679</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Gorgeous Solar Solution</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Finance; Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1281" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1281" t="inlineStr">
+        <is>
+          <t>1 years - 2 years</t>
+        </is>
+      </c>
+      <c r="O1281" t="inlineStr">
+        <is>
+          <t>14 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1281" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aac008eca3b4140b280b679</t>
+        </is>
+      </c>
+      <c r="R1281" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1281" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1281" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1281" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree in Accounting, Accounting &amp; Finance, or a related field of study with relevant work experience out of with 1–2 years of relevant work experience; graduates with strong academic performance are encouraged to apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>6abe4bc1057a8018c68ddcc1</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>IT Support Officer</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Abays Trading PLC</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>ICT; Computer Science and Information Technology</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Sululta</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1282" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1282" t="inlineStr">
+        <is>
+          <t>1 years</t>
+        </is>
+      </c>
+      <c r="O1282" t="inlineStr">
+        <is>
+          <t>14 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1282" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4bc1057a8018c68ddcc1</t>
+        </is>
+      </c>
+      <c r="R1282" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1282" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1282" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1282" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor of Science (BSc) Degree in Information and Communication Technology (ICT), Computer Science, or a related field. The candidate should have a minimum of 1 year of relevant professional experience. Strong technical, computer, analytical, communication, teamwork, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>6abe4bdccccbee18c6bbc331</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Droga Pharma</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Health Care; Pharmacology</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1283" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1283" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1283" t="inlineStr">
+        <is>
+          <t>17 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1283" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4bdccccbee18c6bbc331</t>
+        </is>
+      </c>
+      <c r="R1283" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1283" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1283" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1283" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor of Science (BSc) Degree in Pharmacy or a related field. The candidate should have a minimum of 2 years of relevant professional experience in store management, preferably within a hospital, pharmacy, eye center, clinic, or other healthcare setting. Strong inventory management, pharmaceutical store operations, organizational, attention-to-detail, communication, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>6abd24575a58ae039aef5dac</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Junior Researcher</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>African center for Early Childhood Development</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Social Science; Social Development</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1284" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1284" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1284" t="inlineStr">
+        <is>
+          <t>29 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1284" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd24575a58ae039aef5dac</t>
+        </is>
+      </c>
+      <c r="R1284" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1284" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1284" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1284" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Master’s Degree in Early Childhood Development, Early Childhood Education, Education, Developmental Psychology, Psychology, Public Health, Global Health, Sociology, or a closely related field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>6abe4bda58bb7618c6c23aa5</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Customer Service &amp; Client Coordination Officer</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Tejas Shipping And Logistics Plc</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Finance; Accounting</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1285" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1285" t="inlineStr">
+        <is>
+          <t>3 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1285" t="inlineStr">
+        <is>
+          <t>About 1 Month Left</t>
+        </is>
+      </c>
+      <c r="Q1285" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4bda58bb7618c6c23aa5</t>
+        </is>
+      </c>
+      <c r="R1285" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1285" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1285" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1285" t="inlineStr">
+        <is>
+          <t>The successful candidate should have a minimum of 3–5 years of relevant professional experience in customer service, client coordination, account management, or a related role. Strong written and email communication skills are mandatory, along with excellent customer service, interpersonal, organizational, coordination, and problem-solving skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>6abe4b9616685b18c6b4ed15</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Construction Material Purchaser</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Aymelel Business and Services</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Business; Purchasing &amp; Supply Management</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1286" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1286" t="inlineStr">
+        <is>
+          <t>2 years - 5 years</t>
+        </is>
+      </c>
+      <c r="O1286" t="inlineStr">
+        <is>
+          <t>About 1 Month Left</t>
+        </is>
+      </c>
+      <c r="Q1286" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4b9616685b18c6b4ed15</t>
+        </is>
+      </c>
+      <c r="R1286" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1286" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1286" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1286" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree or Diploma in Supply Chain Management, Logistics, Procurement, Business Administration, or a related field. The candidate should have 2–5 years of relevant professional experience in procurement and logistics, preferably within the real estate or construction sector in Ethiopia. Strong procurement, logistics, supply chain, negotiation, organizational, communication, and problem-solving skills are also required.</t>
         </is>
       </c>
     </row>
@@ -83029,7 +86814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83086,6 +86871,22 @@
         <v>25</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:31:38 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1285</v>
+      </c>
+      <c r="D4" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1286"/>
+  <dimension ref="A1:V1299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86800,6 +86800,931 @@
       <c r="V1286" t="inlineStr">
         <is>
           <t>The successful candidate should possess a Bachelor’s Degree or Diploma in Supply Chain Management, Logistics, Procurement, Business Administration, or a related field. The candidate should have 2–5 years of relevant professional experience in procurement and logistics, preferably within the real estate or construction sector in Ethiopia. Strong procurement, logistics, supply chain, negotiation, organizational, communication, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>6ab4c07ebb5522603f50e380</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Office Engineer</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Cascata Contracting</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Engineering; Civil Engineering</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1287" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K1287" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1287" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1287" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab4c07ebb5522603f50e380</t>
+        </is>
+      </c>
+      <c r="R1287" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1287" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1287" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1287" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree in Civil Engineering with relevant work experience Duties and Responsibilities - Prepare progress reports and payment certificates - Coordinate office and site activities - Follow up project documentation and technical issues - Prepare and review take off and BOQ - Coordinate technical activities between office and site - Review drawings, specifications, and technical documents - Monitor technical progress and resolve issues - Coordinate engineers, consultants, and subcontractors</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>6aba476243d8d3055398b786</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Graduate Assistant II</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Bule Hora University</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Bule Hora</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1288" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1288" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1288" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1288" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aba476243d8d3055398b786</t>
+        </is>
+      </c>
+      <c r="R1288" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1288" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1288" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1288" t="inlineStr">
+        <is>
+          <t>በኢንቫይሮንመንታል ኸልዝ በመጀመሪያ ዲግሪ የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር ዋና ዋና ኃላፊነቶች - የተማሪዎችን የመማር ሂደት መደገፍ - የትምህርት ክፍለ-ጊዜዎች ላይ እገዛ ማድረግ - የተማሪዎችን ስራዎችና ፈተናዎች መመዘን - የማስተማሪያ ቁሳቁሶችን ማዘጋጀት - ከመምህራን ጋር በመተባበር የክፍል ስራዎችን ማከናወን</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>6ab78004c3c3b90a483fb845</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Bule Hora University</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Bule Hora</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1289" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>0 years</t>
+        </is>
+      </c>
+      <c r="O1289" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1289" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab78004c3c3b90a483fb845</t>
+        </is>
+      </c>
+      <c r="R1289" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1289" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1289" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1289" t="inlineStr">
+        <is>
+          <t>በማርኬቲንግ ማኔጅመንት በሁለተኛ ዲግሪ የተመረቀ/ቀች አግባብነት ካለው የስራ ልምድ ጋር ዋና ዋና ኃላፊነቶች - ጥራት ያለው እና በምርምር የተደገፈ ትምህርት ለተማሪዎች ማድረስ - የተማሪዎችን የትምህርት እድገት መከታተልና መገምገም - የተማሪዎችን የምርምር ሥራዎች እና የመመረቂያ ጽሑፎችን በዋና አማካሪነት መምራት - በቅድመ-ምረቃ እና በድህረ-ምረቃ ፕሮግራሞች ጥራት ያለው ትምህርት መስጠት - ዘመናዊ እና ተማሪ-ተኮር የማስተማር ስነ-ዘዴዎችን በተግባር ላይ ማዋል - ለተማሪዎች የአካዳሚክና የሙያ ምክር መስጠት</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>6abcc0677b0b766f9d6f48d0</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>የኢንቪትሮ ዲያግኖስቲክ | (VD) ህክምና መሣርያዎች ግምገማና ፈቃድ ባለሙያ II</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Ethiopian Food and Drug Authority (EFDA)</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Health Care; Health Care Hospitality</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="I1290" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1290" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="N1290" t="inlineStr">
+        <is>
+          <t>Birr 19464/Mon</t>
+        </is>
+      </c>
+      <c r="O1290" t="inlineStr">
+        <is>
+          <t>6 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1290" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abcc0677b0b766f9d6f48d0</t>
+        </is>
+      </c>
+      <c r="R1290" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1290" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1290" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1290" t="inlineStr">
+        <is>
+          <t>በባዮሜዲካል ኢንጂነሪንግ፣ በባዮ ኢንስተሩመንቴሽን ኢንጅነሪንግ፣ ክሊኒካል ኢንጅነሪንግ፣ ማይክሮ ባይሎጂ፣ ኢሚዩኖሎጂ፣ ሄማቶሎጂ፣ ፓርሲቶሎጂ፣ ክሊኒካል ኬሚስትሪ፣ ሞሎኪዩላር ባዮሎጂ ናጀኔቲክስ፣ ቫይሮሎጂ፣ በፋርማሲቲከስ፣ ላቦራቶሪ ማኔጅመንት እና ኳሊቲ አሹራንስ ሁለተኛ ዲግሪ ያለው/ላት አግባብነት ካለው የስራ ልምድ ጋር</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>pCb8C432tZP9g0G</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Real Estate Sales Supervisor</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Central Hills Real Estate Development</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Business; Business Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1291" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1291" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1291" t="inlineStr">
+        <is>
+          <t>29 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1291" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/pCb8C432tZP9g0G</t>
+        </is>
+      </c>
+      <c r="R1291" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1291" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1291" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1291" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in any field of study with relevant work experience. Duties &amp; Responsibilities:﻿ - Supervise and coordinate daily activities of Sales Consultants. - Set daily and weekly sales activities in line with team targets. - Conduct morning planning and afternoon sales reviews. - Monitor lead follow-up, appointments, site visits and sales activities. - Coach sales consultants on prospecting, presentation, negotiation and closing. - Support team members in handling difficult clients and negotiations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>vGRTiXGXlFn1uW</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Real Estate Sales Manager</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Central Hills Real Estate Development</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Business; Business Sales and Marketing</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1292" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1292" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1292" t="inlineStr">
+        <is>
+          <t>29 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1292" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/vGRTiXGXlFn1uW</t>
+        </is>
+      </c>
+      <c r="R1292" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1292" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1292" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1292" t="inlineStr">
+        <is>
+          <t>Bachelor’s Degree in any field of study with relevant work experience. Duties &amp; Responsibilities:﻿ - Develop and implement the company's real estate sales strategy. - Lead and manage the sales team toward agreed business objectives. - Establish sales targets, KPIs and performance standards. - Develop sales pipelines and lead-generation strategies. - Monitor market trends, customer behavior and competitor activities. - Develop strategies for new client acquisition and referral networks. - Review sales performance and identify opportunities for improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>6ab60def0aa4f816cb4133c6</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Personal Assistant to Head of Primary and Early Years School</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Cambridge Academy Ethiopia</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Business; Secretarial, Admin and Clerical</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1293" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1293" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1293" t="inlineStr">
+        <is>
+          <t>About 9 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1293" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab60def0aa4f816cb4133c6</t>
+        </is>
+      </c>
+      <c r="R1293" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1293" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1293" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1293" t="inlineStr">
+        <is>
+          <t>Cambridge Academy Ethiopia seeks a highly professional and discreet Personal Assistant to support the Head of Primary and Early Years School. The role demands a Bachelor’s degree in Business Administration, Secretarial Studies, Office Management, Communications, English, Education or a related field, along with 3–5 years of experience as a PA or senior administrator—preferably within an international school setting. Applicants must demonstrate near‑native proficiency in written and spoken English, advanced skills in Microsoft Office and Google Workspace, and strong minute‑taking, proofreading, and editing abilities. The successful candidate will handle complex diary management, travel arrangements, correspondence drafting, and confidential information with utmost discretion. They will also coordinate meetings, events, and school activities while liaising with parents, staff, senior management, and external stakeholders. Candidates are expected to uphold safeguarding standards, maintain efficient filing systems, support admissions and parent communications, manage budgetary tasks for the Head’s office, and collaborate with other administrative staff across the school. Professional development opportunities and health insurance are provided after probation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>6a9712c2dbc1d748ff29e405</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Junior Assembly Technician (Electric two or three wheeler)</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Dodai Manufacturing</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Engineering; Manufacturing Engineering</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1294" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1294" t="inlineStr">
+        <is>
+          <t>0 years - 1 years</t>
+        </is>
+      </c>
+      <c r="O1294" t="inlineStr">
+        <is>
+          <t>About 9 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1294" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9712c2dbc1d748ff29e405</t>
+        </is>
+      </c>
+      <c r="R1294" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1294" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1294" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1294" t="inlineStr">
+        <is>
+          <t>Dodai Manufacturing Plc is recruiting a Junior Assembly Technician to join its manufacturing team in Addis Ababa, Ethiopia. The role focuses on assembling electric two‑wheelers, ensuring precision and quality through calibration, testing, and maintenance of equipment. Candidates should hold a bachelor’s degree in Mechanical Engineering, Industrial Engineering or related fields (or be a TVET graduate) and possess basic Microsoft Office skills along with strong analytical, communication and time‑management abilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>6a980fd6cbd6f20daed8d86e</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Ethiopian Red Cross Society</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Hospitality; Food Preparation</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1295" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>Diploma</t>
+        </is>
+      </c>
+      <c r="K1295" t="inlineStr">
+        <is>
+          <t>2 years - 6 years</t>
+        </is>
+      </c>
+      <c r="O1295" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1295" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a980fd6cbd6f20daed8d86e</t>
+        </is>
+      </c>
+      <c r="R1295" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1295" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1295" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1295" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a First Degree, Diploma, Level IV, or Level III qualification in Food Preparation, Pastry and Bakery, Culinary Arts, Confectionery, or a related field, along with 2–6 years of relevant professional work experience in food preparation, culinary, or confectionery services, depending on the level of qualification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>6abd2410a96f4d039a2cdd0a</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>3. SENIOR QUANTITY SURVEYOR</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Gift Business Group</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Engineering; Surveying Engineering</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1296" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1296" t="inlineStr">
+        <is>
+          <t>8 years</t>
+        </is>
+      </c>
+      <c r="O1296" t="inlineStr">
+        <is>
+          <t>5 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1296" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd2410a96f4d039a2cdd0a</t>
+        </is>
+      </c>
+      <c r="R1296" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1296" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1296" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1296" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a BSc or MSc Degree in Quantity Surveying or a closely related construction cost-management discipline from a recognized institution. The candidate should have a minimum of 8 years of relevant professional experience for BSc holders or 5 years for MSc holders. Strong quantity surveying, cost management, construction, analytical, numerical, organizational, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>6aa174c7680903243399da8b</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Human Resources (HR) Manager</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Mag School</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Business; Human Resource Management</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1297" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1297" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1297" t="inlineStr">
+        <is>
+          <t>8 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1297" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6aa174c7680903243399da8b</t>
+        </is>
+      </c>
+      <c r="R1297" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1297" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1297" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1297" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Degree in Human Resource Management, Business Administration, Management, or a related field, with a minimum of 5 years of relevant professional experience in human resources. Experience working in a school or educational institution is considered an added advantage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>6abd4eab897a5e3a0f2dd832</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Supply Chain and Procurement Officer</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Segon-Marill International Movers PLC</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Business; Purchasing &amp; Supply Management</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1298" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1298" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1298" t="inlineStr">
+        <is>
+          <t>29 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1298" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abd4eab897a5e3a0f2dd832</t>
+        </is>
+      </c>
+      <c r="R1298" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1298" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1298" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1298" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Procurement, Supply Chain Management, Business Administration, Logistics, Finance, or a related field. A recognized professional procurement certification is considered an added advantage. The candidate should have a minimum of 3 years of relevant professional experience in procurement, sourcing, supplier management, or materials control. Experience in service operations, logistics, transport, or fleet management is considered an added advantage. Strong procurement, supplier management, analytical, negotiation, organizational, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>6abe4b8fb93efe18c65bd65b</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>SENIOR NETWORK ENGINEER</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Next General Trading</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Engineering; Network Engineering</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1299" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1299" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="O1299" t="inlineStr">
+        <is>
+          <t>About 1 Month Left</t>
+        </is>
+      </c>
+      <c r="Q1299" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6abe4b8fb93efe18c65bd65b</t>
+        </is>
+      </c>
+      <c r="R1299" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1299" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:21:37 UTC</t>
+        </is>
+      </c>
+      <c r="U1299" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1299" t="inlineStr">
+        <is>
+          <t>The successful candidate should have more than 6 years of relevant hands-on professional experience in network engineering and hardware support. The candidate should possess a CCNA/CCNP or HCIA/HCIP certification. Strong knowledge of networking protocols, network equipment, installation, configuration, maintenance, and troubleshooting is also required.</t>
         </is>
       </c>
     </row>
@@ -86814,7 +87739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86887,6 +87812,22 @@
         <v>26</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:23:02 UTC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1298</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1299"/>
+  <dimension ref="A1:V1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87725,6 +87725,431 @@
       <c r="V1299" t="inlineStr">
         <is>
           <t>The successful candidate should have more than 6 years of relevant hands-on professional experience in network engineering and hardware support. The candidate should possess a CCNA/CCNP or HCIA/HCIP certification. Strong knowledge of networking protocols, network equipment, installation, configuration, maintenance, and troubleshooting is also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>6a9712d0a7b65f48ffce97dd</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Customer Experience (CX) Manager</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Dodai Manufacturing</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Business; Business Administration</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1300" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1300" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1300" t="inlineStr">
+        <is>
+          <t>About 8 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1300" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9712d0a7b65f48ffce97dd</t>
+        </is>
+      </c>
+      <c r="R1300" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1300" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U1300" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1300" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Business Administration, Marketing, Engineering, or a related field from a recognized institution. The candidate should have a minimum of 5 years of relevant professional experience in customer experience, after-sales services, or service operations, preferably within the automotive, mobility, telecommunications, or related sectors. Strong customer relationship management, communication, problem-solving, service coordination, analytical, and interpersonal skills are required, with the ability to improve customer satisfaction, manage service-related issues, and support effective after-sales operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>6ab146904ca3182b138e9609</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Community Facilitator</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Hope for justice (former Retrak Ethiopia)</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Social Science; Social Science and Community</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Kebri Beyah</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1301" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1301" t="inlineStr">
+        <is>
+          <t>1 years</t>
+        </is>
+      </c>
+      <c r="O1301" t="inlineStr">
+        <is>
+          <t>About 8 Hours Left</t>
+        </is>
+      </c>
+      <c r="Q1301" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab146904ca3182b138e9609</t>
+        </is>
+      </c>
+      <c r="R1301" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1301" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U1301" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1301" t="inlineStr">
+        <is>
+          <t>The successful candidate should have completed Grade 12 or above. The candidate should have a minimum of 1 year of relevant professional experience in community engagement, preferably with an international NGO. Experience in Self-Help Group (SHG) facilitation or community facilitation is also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>6ab3e988e33a043771d0d9b5</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>MERL Coordinator (Women Peace Security)</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Plan International Ethiopia</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Finance; Economics</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1302" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1302" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="O1302" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1302" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab3e988e33a043771d0d9b5</t>
+        </is>
+      </c>
+      <c r="R1302" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1302" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U1302" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1302" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Statistics, Economics, or a related field. The candidate should have a minimum of 5 years of progressive professional experience in Monitoring, Evaluation, Research, and Learning (MERL) coordination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>6a97e61178710d526819e7f8</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Sunshine Retail</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Business; Marketing Management</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1303" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1303" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="O1303" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1303" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a97e61178710d526819e7f8</t>
+        </is>
+      </c>
+      <c r="R1303" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1303" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U1303" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1303" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a minimum of 6 years of proven professional experience in Hospitality, FMCG Sales, or a related sales role. The candidate should demonstrate strong sales and negotiation skills, with the ability to develop business opportunities, achieve sales targets, build and maintain strong customer relationships, and effectively promote products or services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>6ab395707fc31243f5cd01fb</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Architectural Designer</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>FG BUSINESS GROUP</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Engineering; Architectural Engineering</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1304" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1304" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1304" t="inlineStr">
+        <is>
+          <t>3 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1304" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab395707fc31243f5cd01fb</t>
+        </is>
+      </c>
+      <c r="R1304" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1304" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U1304" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1304" t="inlineStr">
+        <is>
+          <t>The successful candidate should possess a Bachelor’s Degree in Architecture, Architectural Engineering, Construction Design, or a related field. The candidate should have a minimum of 3 years of relevant professional experience in architectural design, construction design, or a related field. Strong architectural, technical, design, analytical, communication, and problem-solving skills are also required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>6a9a5e70752466217ea718bb</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Multi-Skilled Technician Supervisor</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>The First GROUP HOSPITALITY</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Low and Medium Skilled Worker; Maintenance</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1305" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="K1305" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="O1305" t="inlineStr">
+        <is>
+          <t>3 Days Left</t>
+        </is>
+      </c>
+      <c r="Q1305" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6a9a5e70752466217ea718bb</t>
+        </is>
+      </c>
+      <c r="R1305" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1305" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:36:29 UTC</t>
+        </is>
+      </c>
+      <c r="U1305" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1305" t="inlineStr">
+        <is>
+          <t>Level III Certificate from a recognized Technical and Vocational Education and Training (TVET) institution in Maintenance, Electrical Work, Carpentry, Water Engineering, Construction Management, or a related technical field, with a minimum of 2 years of relevant work experience; OR Level IV Certificate in a relevant field with a minimum of 1 year of relevant work experience as a Multi-Skilled Technician or in a similar position.</t>
         </is>
       </c>
     </row>
@@ -87739,7 +88164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87828,6 +88253,22 @@
         <v>26</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:38:03 UTC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1304</v>
+      </c>
+      <c r="D6" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1305"/>
+  <dimension ref="A1:V1306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88150,6 +88150,81 @@
       <c r="V1305" t="inlineStr">
         <is>
           <t>Level III Certificate from a recognized Technical and Vocational Education and Training (TVET) institution in Maintenance, Electrical Work, Carpentry, Water Engineering, Construction Management, or a related technical field, with a minimum of 2 years of relevant work experience; OR Level IV Certificate in a relevant field with a minimum of 1 year of relevant work experience as a Multi-Skilled Technician or in a similar position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>6ab60df2fbf7a916cbb94863</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Primary School Librarian</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Cambridge Academy Ethiopia</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Education; Teaching</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Addis Ababa</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="I1306" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1306" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+      <c r="K1306" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="O1306" t="inlineStr">
+        <is>
+          <t>1 Day Left</t>
+        </is>
+      </c>
+      <c r="Q1306" t="inlineStr">
+        <is>
+          <t>https://hahu.jobs/jobs/6ab60df2fbf7a916cbb94863</t>
+        </is>
+      </c>
+      <c r="R1306" t="inlineStr">
+        <is>
+          <t>HaHuJobs</t>
+        </is>
+      </c>
+      <c r="T1306" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:57:57 UTC</t>
+        </is>
+      </c>
+      <c r="U1306" t="inlineStr">
+        <is>
+          <t>listing_only</t>
+        </is>
+      </c>
+      <c r="V1306" t="inlineStr">
+        <is>
+          <t>Bachelor's Degree in Library and Information Science, Education, English, or a related field with relevant work experience</t>
         </is>
       </c>
     </row>
@@ -88164,7 +88239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88269,6 +88344,22 @@
         <v>26</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:59:29 UTC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -88239,7 +88239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88360,6 +88360,22 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:30:55 UTC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -88239,7 +88239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88376,6 +88376,22 @@
         <v>26</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:50:34 UTC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hahujobs_tracker.xlsx
+++ b/hahujobs_tracker.xlsx
@@ -88239,7 +88239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88392,6 +88392,22 @@
         <v>26</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:06:16 UTC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
